--- a/HDR_files/Area country list.xlsx
+++ b/HDR_files/Area country list.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Me\Documents\UC_MASTER APPLIED DATA SCIENCE\DATA601\PROJECT\myWVSapp\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Me\Documents\UC_MASTER APPLIED DATA SCIENCE\DATA601\PROJECT\GitHub_WVsa_Original version\WorldView\HDR_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CD80B7-9555-4BAF-846B-DE9BE19F8BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8915B233-4504-4233-9E5C-C3AAD291B4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" tabRatio="717" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hdi_groups" sheetId="2" r:id="rId1"/>
     <sheet name="regions" sheetId="4" r:id="rId2"/>
-    <sheet name="special_groups" sheetId="7" r:id="rId3"/>
+    <sheet name="special_groups" sheetId="10" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="240">
   <si>
     <t>Afghanistan</t>
   </si>
@@ -728,6 +728,36 @@
   </si>
   <si>
     <t>area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebanon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">United Arab Emirates </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myanmar </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syrian Arab Republic </t>
+  </si>
+  <si>
+    <t>Republic of Moldov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamaica </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sierra Leone</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> United Republic of Tanzania</t>
+  </si>
+  <si>
+    <t>DCs</t>
   </si>
 </sst>
 </file>
@@ -3888,8 +3918,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568CAD53-5BC3-41CD-9D8E-3E76380216BC}">
-  <dimension ref="A1:F122"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B1130A3-902C-48B6-95F3-941E587781C1}">
+  <dimension ref="A1:F273"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.75">
@@ -4872,6 +4902,1214 @@
         <v>155</v>
       </c>
     </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A123" t="s">
+        <v>239</v>
+      </c>
+      <c r="B123" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A124" t="s">
+        <v>239</v>
+      </c>
+      <c r="B124" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A125" t="s">
+        <v>239</v>
+      </c>
+      <c r="B125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A126" t="s">
+        <v>239</v>
+      </c>
+      <c r="B126" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A127" t="s">
+        <v>239</v>
+      </c>
+      <c r="B127" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A128" t="s">
+        <v>239</v>
+      </c>
+      <c r="B128" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A129" t="s">
+        <v>239</v>
+      </c>
+      <c r="B129" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A130" t="s">
+        <v>239</v>
+      </c>
+      <c r="B130" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A131" t="s">
+        <v>239</v>
+      </c>
+      <c r="B131" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A132" t="s">
+        <v>239</v>
+      </c>
+      <c r="B132" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A133" t="s">
+        <v>239</v>
+      </c>
+      <c r="B133" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A134" t="s">
+        <v>239</v>
+      </c>
+      <c r="B134" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A135" t="s">
+        <v>239</v>
+      </c>
+      <c r="B135" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A136" t="s">
+        <v>239</v>
+      </c>
+      <c r="B136" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A137" t="s">
+        <v>239</v>
+      </c>
+      <c r="B137" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A138" t="s">
+        <v>239</v>
+      </c>
+      <c r="B138" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A139" t="s">
+        <v>239</v>
+      </c>
+      <c r="B139" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A140" t="s">
+        <v>239</v>
+      </c>
+      <c r="B140" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A141" t="s">
+        <v>239</v>
+      </c>
+      <c r="B141" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A142" t="s">
+        <v>239</v>
+      </c>
+      <c r="B142" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A143" t="s">
+        <v>239</v>
+      </c>
+      <c r="B143" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A144" t="s">
+        <v>239</v>
+      </c>
+      <c r="B144" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A145" t="s">
+        <v>239</v>
+      </c>
+      <c r="B145" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A146" t="s">
+        <v>239</v>
+      </c>
+      <c r="B146" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A147" t="s">
+        <v>239</v>
+      </c>
+      <c r="B147" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A148" t="s">
+        <v>239</v>
+      </c>
+      <c r="B148" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A149" t="s">
+        <v>239</v>
+      </c>
+      <c r="B149" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A150" t="s">
+        <v>239</v>
+      </c>
+      <c r="B150" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A151" t="s">
+        <v>239</v>
+      </c>
+      <c r="B151" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A152" t="s">
+        <v>239</v>
+      </c>
+      <c r="B152" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A153" t="s">
+        <v>239</v>
+      </c>
+      <c r="B153" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A154" t="s">
+        <v>239</v>
+      </c>
+      <c r="B154" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A155" t="s">
+        <v>239</v>
+      </c>
+      <c r="B155" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A156" t="s">
+        <v>239</v>
+      </c>
+      <c r="B156" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A157" t="s">
+        <v>239</v>
+      </c>
+      <c r="B157" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A158" t="s">
+        <v>239</v>
+      </c>
+      <c r="B158" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A159" t="s">
+        <v>239</v>
+      </c>
+      <c r="B159" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A160" t="s">
+        <v>239</v>
+      </c>
+      <c r="B160" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A161" t="s">
+        <v>239</v>
+      </c>
+      <c r="B161" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A162" t="s">
+        <v>239</v>
+      </c>
+      <c r="B162" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A163" t="s">
+        <v>239</v>
+      </c>
+      <c r="B163" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A164" t="s">
+        <v>239</v>
+      </c>
+      <c r="B164" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A165" t="s">
+        <v>239</v>
+      </c>
+      <c r="B165" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A166" t="s">
+        <v>239</v>
+      </c>
+      <c r="B166" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A167" t="s">
+        <v>239</v>
+      </c>
+      <c r="B167" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A168" t="s">
+        <v>239</v>
+      </c>
+      <c r="B168" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A169" t="s">
+        <v>239</v>
+      </c>
+      <c r="B169" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A170" t="s">
+        <v>239</v>
+      </c>
+      <c r="B170" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A171" t="s">
+        <v>239</v>
+      </c>
+      <c r="B171" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A172" t="s">
+        <v>239</v>
+      </c>
+      <c r="B172" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A173" t="s">
+        <v>239</v>
+      </c>
+      <c r="B173" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A174" t="s">
+        <v>239</v>
+      </c>
+      <c r="B174" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A175" t="s">
+        <v>239</v>
+      </c>
+      <c r="B175" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A176" t="s">
+        <v>239</v>
+      </c>
+      <c r="B176" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A177" t="s">
+        <v>239</v>
+      </c>
+      <c r="B177" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A178" t="s">
+        <v>239</v>
+      </c>
+      <c r="B178" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A179" t="s">
+        <v>239</v>
+      </c>
+      <c r="B179" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A180" t="s">
+        <v>239</v>
+      </c>
+      <c r="B180" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A181" t="s">
+        <v>239</v>
+      </c>
+      <c r="B181" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A182" t="s">
+        <v>239</v>
+      </c>
+      <c r="B182" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A183" t="s">
+        <v>239</v>
+      </c>
+      <c r="B183" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A184" t="s">
+        <v>239</v>
+      </c>
+      <c r="B184" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A185" t="s">
+        <v>239</v>
+      </c>
+      <c r="B185" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A186" t="s">
+        <v>239</v>
+      </c>
+      <c r="B186" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A187" t="s">
+        <v>239</v>
+      </c>
+      <c r="B187" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A188" t="s">
+        <v>239</v>
+      </c>
+      <c r="B188" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A189" t="s">
+        <v>239</v>
+      </c>
+      <c r="B189" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A190" t="s">
+        <v>239</v>
+      </c>
+      <c r="B190" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A191" t="s">
+        <v>239</v>
+      </c>
+      <c r="B191" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A192" t="s">
+        <v>239</v>
+      </c>
+      <c r="B192" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A193" t="s">
+        <v>239</v>
+      </c>
+      <c r="B193" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A194" t="s">
+        <v>239</v>
+      </c>
+      <c r="B194" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A195" t="s">
+        <v>239</v>
+      </c>
+      <c r="B195" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A196" t="s">
+        <v>239</v>
+      </c>
+      <c r="B196" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A197" t="s">
+        <v>239</v>
+      </c>
+      <c r="B197" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A198" t="s">
+        <v>239</v>
+      </c>
+      <c r="B198" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A199" t="s">
+        <v>239</v>
+      </c>
+      <c r="B199" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A200" t="s">
+        <v>239</v>
+      </c>
+      <c r="B200" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A201" t="s">
+        <v>239</v>
+      </c>
+      <c r="B201" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A202" t="s">
+        <v>239</v>
+      </c>
+      <c r="B202" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A203" t="s">
+        <v>239</v>
+      </c>
+      <c r="B203" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A204" t="s">
+        <v>239</v>
+      </c>
+      <c r="B204" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A205" t="s">
+        <v>239</v>
+      </c>
+      <c r="B205" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A206" t="s">
+        <v>239</v>
+      </c>
+      <c r="B206" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A207" t="s">
+        <v>239</v>
+      </c>
+      <c r="B207" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A208" t="s">
+        <v>239</v>
+      </c>
+      <c r="B208" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A209" t="s">
+        <v>239</v>
+      </c>
+      <c r="B209" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A210" t="s">
+        <v>239</v>
+      </c>
+      <c r="B210" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A211" t="s">
+        <v>239</v>
+      </c>
+      <c r="B211" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A212" t="s">
+        <v>239</v>
+      </c>
+      <c r="B212" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A213" t="s">
+        <v>239</v>
+      </c>
+      <c r="B213" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A214" t="s">
+        <v>239</v>
+      </c>
+      <c r="B214" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A215" t="s">
+        <v>239</v>
+      </c>
+      <c r="B215" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A216" t="s">
+        <v>239</v>
+      </c>
+      <c r="B216" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A217" t="s">
+        <v>239</v>
+      </c>
+      <c r="B217" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A218" t="s">
+        <v>239</v>
+      </c>
+      <c r="B218" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A219" t="s">
+        <v>239</v>
+      </c>
+      <c r="B219" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A220" t="s">
+        <v>239</v>
+      </c>
+      <c r="B220" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A221" t="s">
+        <v>239</v>
+      </c>
+      <c r="B221" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A222" t="s">
+        <v>239</v>
+      </c>
+      <c r="B222" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A223" t="s">
+        <v>239</v>
+      </c>
+      <c r="B223" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A224" t="s">
+        <v>239</v>
+      </c>
+      <c r="B224" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A225" t="s">
+        <v>239</v>
+      </c>
+      <c r="B225" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A226" t="s">
+        <v>239</v>
+      </c>
+      <c r="B226" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A227" t="s">
+        <v>239</v>
+      </c>
+      <c r="B227" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A228" t="s">
+        <v>239</v>
+      </c>
+      <c r="B228" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A229" t="s">
+        <v>239</v>
+      </c>
+      <c r="B229" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A230" t="s">
+        <v>239</v>
+      </c>
+      <c r="B230" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A231" t="s">
+        <v>239</v>
+      </c>
+      <c r="B231" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A232" t="s">
+        <v>239</v>
+      </c>
+      <c r="B232" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A233" t="s">
+        <v>239</v>
+      </c>
+      <c r="B233" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A234" t="s">
+        <v>239</v>
+      </c>
+      <c r="B234" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A235" t="s">
+        <v>239</v>
+      </c>
+      <c r="B235" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A236" t="s">
+        <v>239</v>
+      </c>
+      <c r="B236" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A237" t="s">
+        <v>239</v>
+      </c>
+      <c r="B237" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A238" t="s">
+        <v>239</v>
+      </c>
+      <c r="B238" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A239" t="s">
+        <v>239</v>
+      </c>
+      <c r="B239" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A240" t="s">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A241" t="s">
+        <v>239</v>
+      </c>
+      <c r="B241" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A242" t="s">
+        <v>239</v>
+      </c>
+      <c r="B242" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A243" t="s">
+        <v>239</v>
+      </c>
+      <c r="B243" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A244" t="s">
+        <v>239</v>
+      </c>
+      <c r="B244" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A245" t="s">
+        <v>239</v>
+      </c>
+      <c r="B245" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A246" t="s">
+        <v>239</v>
+      </c>
+      <c r="B246" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A247" t="s">
+        <v>239</v>
+      </c>
+      <c r="B247" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A248" t="s">
+        <v>239</v>
+      </c>
+      <c r="B248" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A249" t="s">
+        <v>239</v>
+      </c>
+      <c r="B249" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A250" t="s">
+        <v>239</v>
+      </c>
+      <c r="B250" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A251" t="s">
+        <v>239</v>
+      </c>
+      <c r="B251" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A252" t="s">
+        <v>239</v>
+      </c>
+      <c r="B252" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A253" t="s">
+        <v>239</v>
+      </c>
+      <c r="B253" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A254" t="s">
+        <v>239</v>
+      </c>
+      <c r="B254" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A255" t="s">
+        <v>239</v>
+      </c>
+      <c r="B255" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A256" t="s">
+        <v>239</v>
+      </c>
+      <c r="B256" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A257" t="s">
+        <v>239</v>
+      </c>
+      <c r="B257" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A258" t="s">
+        <v>239</v>
+      </c>
+      <c r="B258" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A259" t="s">
+        <v>239</v>
+      </c>
+      <c r="B259" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A260" t="s">
+        <v>239</v>
+      </c>
+      <c r="B260" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A261" t="s">
+        <v>239</v>
+      </c>
+      <c r="B261" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A262" t="s">
+        <v>239</v>
+      </c>
+      <c r="B262" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A263" t="s">
+        <v>239</v>
+      </c>
+      <c r="B263" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A264" t="s">
+        <v>239</v>
+      </c>
+      <c r="B264" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A265" t="s">
+        <v>239</v>
+      </c>
+      <c r="B265" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A266" t="s">
+        <v>239</v>
+      </c>
+      <c r="B266" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A267" t="s">
+        <v>239</v>
+      </c>
+      <c r="B267" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A268" t="s">
+        <v>239</v>
+      </c>
+      <c r="B268" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A269" t="s">
+        <v>239</v>
+      </c>
+      <c r="B269" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A270" t="s">
+        <v>239</v>
+      </c>
+      <c r="B270" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A271" t="s">
+        <v>239</v>
+      </c>
+      <c r="B271" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A272" t="s">
+        <v>239</v>
+      </c>
+      <c r="B272" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A273" t="s">
+        <v>239</v>
+      </c>
+      <c r="B273" t="s">
+        <v>157</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
